--- a/docs/PD_RTM_v1.0.xlsx
+++ b/docs/PD_RTM_v1.0.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="360">
   <si>
     <t>PulseDesk — Requirements Traceability Matrix</t>
   </si>
@@ -595,6 +595,123 @@
     <t>TC-F-031</t>
   </si>
   <si>
+    <t>FUN-032</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>Serve the same dashboard as an installable web app on Android, iOS and desktop browsers</t>
+  </si>
+  <si>
+    <t>Public user</t>
+  </si>
+  <si>
+    <t>Charter §3.8</t>
+  </si>
+  <si>
+    <t>SDD §10.2</t>
+  </si>
+  <si>
+    <t>TC-F-032</t>
+  </si>
+  <si>
+    <t>FUN-033</t>
+  </si>
+  <si>
+    <t>Cache the app shell in a service worker so it opens without a connection</t>
+  </si>
+  <si>
+    <t>SDD §10.3</t>
+  </si>
+  <si>
+    <t>TC-F-033</t>
+  </si>
+  <si>
+    <t>FUN-034</t>
+  </si>
+  <si>
+    <t>Route web market data through an edge worker because browsers cannot call the upstreams directly</t>
+  </si>
+  <si>
+    <t>SDD §10.1</t>
+  </si>
+  <si>
+    <t>TC-F-034</t>
+  </si>
+  <si>
+    <t>FUN-035</t>
+  </si>
+  <si>
+    <t>Keep web holdings in browser local storage so the web build needs no account either</t>
+  </si>
+  <si>
+    <t>TC-F-035</t>
+  </si>
+  <si>
+    <t>FUN-036</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>Count app opens, distinct devices per day and devices active in the last five minutes without any login</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Charter §3.9</t>
+  </si>
+  <si>
+    <t>SDD §11.1</t>
+  </si>
+  <si>
+    <t>TC-F-036</t>
+  </si>
+  <si>
+    <t>DPDP §4</t>
+  </si>
+  <si>
+    <t>FUN-037</t>
+  </si>
+  <si>
+    <t>Present those counts on a private dashboard gated by a shared key, with a 30-day trend, country and platform split</t>
+  </si>
+  <si>
+    <t>SDD §11.2</t>
+  </si>
+  <si>
+    <t>TC-F-037</t>
+  </si>
+  <si>
+    <t>FUN-038</t>
+  </si>
+  <si>
+    <t>Publish the Windows installer and portable build automatically from a version tag</t>
+  </si>
+  <si>
+    <t>SDD §10.4</t>
+  </si>
+  <si>
+    <t>TC-F-038</t>
+  </si>
+  <si>
+    <t>FUN-039</t>
+  </si>
+  <si>
+    <t>Show a subtle author credit in the status bar, tray menu, manifest and packaged metadata</t>
+  </si>
+  <si>
+    <t>Charter §3.10</t>
+  </si>
+  <si>
+    <t>SDD §5.1</t>
+  </si>
+  <si>
+    <t>TC-F-039</t>
+  </si>
+  <si>
     <t>SEC-001</t>
   </si>
   <si>
@@ -736,6 +853,57 @@
     <t>TC-S-010</t>
   </si>
   <si>
+    <t>SEC-011</t>
+  </si>
+  <si>
+    <t>The statistics endpoint is refused without the shared key held as a worker secret</t>
+  </si>
+  <si>
+    <t>TC-S-011</t>
+  </si>
+  <si>
+    <t>SEC-012</t>
+  </si>
+  <si>
+    <t>No IP address, cookie, email or account is stored — only a random client-generated id, coarse country and platform</t>
+  </si>
+  <si>
+    <t>TC-S-012</t>
+  </si>
+  <si>
+    <t>SEC-013</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>The worker holds no upstream credentials and accepts only its documented routes</t>
+  </si>
+  <si>
+    <t>OWASP A05</t>
+  </si>
+  <si>
+    <t>TC-S-013</t>
+  </si>
+  <si>
+    <t>SEC-014</t>
+  </si>
+  <si>
+    <t>Visitor identifiers are sanitised and length-capped before they reach the database</t>
+  </si>
+  <si>
+    <t>TC-S-014</t>
+  </si>
+  <si>
+    <t>SEC-015</t>
+  </si>
+  <si>
+    <t>The web build declares a content security policy that allows connections only to its own origin and the configured worker</t>
+  </si>
+  <si>
+    <t>TC-S-015</t>
+  </si>
+  <si>
     <t>NFR-001</t>
   </si>
   <si>
@@ -787,9 +955,6 @@
     <t>Zero paid services, subscriptions or API keys</t>
   </si>
   <si>
-    <t>Owner</t>
-  </si>
-  <si>
     <t>Charter §2</t>
   </si>
   <si>
@@ -854,6 +1019,36 @@
   </si>
   <si>
     <t>TC-N-010</t>
+  </si>
+  <si>
+    <t>NFR-011</t>
+  </si>
+  <si>
+    <t>Edge caching holds worker traffic inside the free allowance at ten thousand daily users</t>
+  </si>
+  <si>
+    <t>TC-N-011</t>
+  </si>
+  <si>
+    <t>NFR-012</t>
+  </si>
+  <si>
+    <t>The phone layout fits a 375 px viewport with no horizontal scrolling and safe-area padding</t>
+  </si>
+  <si>
+    <t>TC-N-012</t>
+  </si>
+  <si>
+    <t>NFR-013</t>
+  </si>
+  <si>
+    <t>Hosting, delivery and analytics stay at zero recurring cost</t>
+  </si>
+  <si>
+    <t>SDD §10.5</t>
+  </si>
+  <si>
+    <t>TC-N-013</t>
   </si>
   <si>
     <t>Role</t>
@@ -1644,7 +1839,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2780,6 +2975,286 @@
         <v>50</v>
       </c>
     </row>
+    <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2789,7 +3264,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2842,13 +3317,13 @@
     </row>
     <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>78</v>
@@ -2860,16 +3335,16 @@
         <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>50</v>
@@ -2877,13 +3352,13 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>78</v>
@@ -2895,16 +3370,16 @@
         <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>50</v>
@@ -2912,13 +3387,13 @@
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>78</v>
@@ -2930,16 +3405,16 @@
         <v>30</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>50</v>
@@ -2947,13 +3422,13 @@
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>78</v>
@@ -2965,7 +3440,7 @@
         <v>30</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>126</v>
@@ -2974,7 +3449,7 @@
         <v>127</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>50</v>
@@ -2982,13 +3457,13 @@
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>78</v>
@@ -3000,16 +3475,16 @@
         <v>30</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>50</v>
@@ -3017,13 +3492,13 @@
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>78</v>
@@ -3035,16 +3510,16 @@
         <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
@@ -3052,13 +3527,13 @@
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>68</v>
@@ -3070,16 +3545,16 @@
         <v>30</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>50</v>
@@ -3087,13 +3562,13 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>78</v>
@@ -3105,16 +3580,16 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>50</v>
@@ -3122,13 +3597,13 @@
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>78</v>
@@ -3140,16 +3615,16 @@
         <v>30</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>50</v>
@@ -3157,16 +3632,16 @@
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>23</v>
@@ -3175,18 +3650,193 @@
         <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="C12" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3199,7 +3849,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3252,13 +3902,13 @@
     </row>
     <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>68</v>
@@ -3270,13 +3920,13 @@
         <v>34</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>72</v>
@@ -3287,13 +3937,13 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>68</v>
@@ -3305,13 +3955,13 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>72</v>
@@ -3322,13 +3972,13 @@
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>68</v>
@@ -3340,13 +3990,13 @@
         <v>34</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>72</v>
@@ -3357,13 +4007,13 @@
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>307</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>78</v>
@@ -3375,13 +4025,13 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>72</v>
@@ -3392,16 +4042,16 @@
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>19</v>
@@ -3410,13 +4060,13 @@
         <v>34</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>72</v>
@@ -3427,13 +4077,13 @@
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>261</v>
+        <v>316</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>68</v>
@@ -3445,16 +4095,16 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>190</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>263</v>
+        <v>318</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
@@ -3462,13 +4112,13 @@
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>68</v>
@@ -3480,16 +4130,16 @@
         <v>34</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>266</v>
+        <v>321</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>267</v>
+        <v>322</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>263</v>
+        <v>318</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>50</v>
@@ -3497,13 +4147,13 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>324</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>68</v>
@@ -3515,13 +4165,13 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>72</v>
@@ -3532,16 +4182,16 @@
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>23</v>
@@ -3550,13 +4200,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>72</v>
@@ -3567,13 +4217,13 @@
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>78</v>
@@ -3585,18 +4235,123 @@
         <v>34</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>72</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3618,7 +4373,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>279</v>
+        <v>344</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>59</v>
@@ -3629,7 +4384,7 @@
         <v>68</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>280</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3637,7 +4392,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -3645,23 +4400,23 @@
         <v>149</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>282</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>283</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>284</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3669,7 +4424,7 @@
         <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>285</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -3690,15 +4445,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>286</v>
+        <v>351</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>287</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="B2" s="5">
         <f>COUNTA('Functional RTM'!A2:A200)</f>
@@ -3706,7 +4461,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>354</v>
       </c>
       <c r="B3" s="5">
         <f>COUNTA('Security RTM'!A2:A200)</f>
@@ -3714,7 +4469,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTA('NFR RTM'!A2:A200)</f>
@@ -3722,7 +4477,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>356</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTA('Functional RTM'!A2:A200)+COUNTA('Security RTM'!A2:A200)+COUNTA('NFR RTM'!A2:A200)</f>
@@ -3730,7 +4485,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Functional RTM'!E2:E200,"M")+COUNTIF('Security RTM'!E2:E200,"M")+COUNTIF('NFR RTM'!E2:E200,"M")</f>
@@ -3746,7 +4501,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Functional RTM'!K2:K200,"Developed")+COUNTIF('Security RTM'!K2:K200,"Developed")+COUNTIF('NFR RTM'!K2:K200,"Developed")</f>
@@ -3754,7 +4509,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="B9" s="5">
         <f>ROUND((COUNTIF('Functional RTM'!K2:K200,"Verified")+COUNTIF('Security RTM'!K2:K200,"Verified")+COUNTIF('NFR RTM'!K2:K200,"Verified"))/(COUNTA('Functional RTM'!A2:A200)+COUNTA('Security RTM'!A2:A200)+COUNTA('NFR RTM'!A2:A200))*100,1)</f>

--- a/docs/PD_RTM_v1.0.xlsx
+++ b/docs/PD_RTM_v1.0.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="409">
   <si>
     <t>PulseDesk — Requirements Traceability Matrix</t>
   </si>
@@ -700,7 +700,7 @@
     <t>FUN-039</t>
   </si>
   <si>
-    <t>Show a subtle author credit in the status bar, tray menu, manifest and packaged metadata</t>
+    <t>Show a subtle author credit in the status bar, title bar, tray menu, manifest and packaged metadata</t>
   </si>
   <si>
     <t>Charter §3.10</t>
@@ -710,6 +710,153 @@
   </si>
   <si>
     <t>TC-F-039</t>
+  </si>
+  <si>
+    <t>FUN-040</t>
+  </si>
+  <si>
+    <t>Offer a type-ahead list of matching companies and tickers as the user types a name</t>
+  </si>
+  <si>
+    <t>SDD §4.9</t>
+  </si>
+  <si>
+    <t>TC-F-040</t>
+  </si>
+  <si>
+    <t>FUN-041</t>
+  </si>
+  <si>
+    <t>Let the user say the purchase was "right now" or pick an exact past date and time</t>
+  </si>
+  <si>
+    <t>SDD §4.10</t>
+  </si>
+  <si>
+    <t>TC-F-041</t>
+  </si>
+  <si>
+    <t>FUN-042</t>
+  </si>
+  <si>
+    <t>Fill the buy price automatically from the market price at the chosen moment, widening to the nearest trading time when markets were shut</t>
+  </si>
+  <si>
+    <t>TC-F-042</t>
+  </si>
+  <si>
+    <t>FUN-043</t>
+  </si>
+  <si>
+    <t>Preview invested amount and the gain or loss against the live price before the holding is saved</t>
+  </si>
+  <si>
+    <t>TC-F-043</t>
+  </si>
+  <si>
+    <t>FUN-044</t>
+  </si>
+  <si>
+    <t>Allow the auto-filled price to be overridden and label it as the user’s own figure</t>
+  </si>
+  <si>
+    <t>TC-F-044</t>
+  </si>
+  <si>
+    <t>FUN-045</t>
+  </si>
+  <si>
+    <t>Record the purchase timestamp and show holding age and since-date on each row</t>
+  </si>
+  <si>
+    <t>TC-F-045</t>
+  </si>
+  <si>
+    <t>FUN-046</t>
+  </si>
+  <si>
+    <t>Offer a one-click INR/USD switch beside the full base-currency list</t>
+  </si>
+  <si>
+    <t>TC-F-046</t>
+  </si>
+  <si>
+    <t>FUN-047</t>
+  </si>
+  <si>
+    <t>Place the portfolio first on the dashboard, across the full width</t>
+  </si>
+  <si>
+    <t>TC-F-047</t>
+  </si>
+  <si>
+    <t>FUN-048</t>
+  </si>
+  <si>
+    <t>Popular</t>
+  </si>
+  <si>
+    <t>List widely-held large caps ranked by 1-year annualised volatility, with a plain-English steadiness band and 1-year return</t>
+  </si>
+  <si>
+    <t>Charter §3.11</t>
+  </si>
+  <si>
+    <t>SDD §4.11</t>
+  </si>
+  <si>
+    <t>TC-F-048</t>
+  </si>
+  <si>
+    <t>FUN-049</t>
+  </si>
+  <si>
+    <t>Filter that list by India or US and add any row straight into the portfolio</t>
+  </si>
+  <si>
+    <t>TC-F-049</t>
+  </si>
+  <si>
+    <t>FUN-050</t>
+  </si>
+  <si>
+    <t>Offer a most-bought view ranked by 24-hour turnover alongside the 5-hour pump view</t>
+  </si>
+  <si>
+    <t>TC-F-050</t>
+  </si>
+  <si>
+    <t>FUN-051</t>
+  </si>
+  <si>
+    <t>Provide a full-screen control in the title bar and on F11</t>
+  </si>
+  <si>
+    <t>TC-F-051</t>
+  </si>
+  <si>
+    <t>FUN-052</t>
+  </si>
+  <si>
+    <t>Ship the worker as one pasteable file so publishing needs no command line</t>
+  </si>
+  <si>
+    <t>Charter §3.12</t>
+  </si>
+  <si>
+    <t>SDD §10.6</t>
+  </si>
+  <si>
+    <t>TC-F-052</t>
+  </si>
+  <si>
+    <t>FUN-053</t>
+  </si>
+  <si>
+    <t>Provide double-click launchers and a click-by-click publishing guide for a non-technical operator</t>
+  </si>
+  <si>
+    <t>TC-F-053</t>
   </si>
   <si>
     <t>SEC-001</t>
@@ -1839,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3252,6 +3399,496 @@
         <v>72</v>
       </c>
       <c r="K40" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K54" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3317,13 +3954,13 @@
     </row>
     <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>78</v>
@@ -3335,16 +3972,16 @@
         <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>50</v>
@@ -3352,13 +3989,13 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>78</v>
@@ -3370,16 +4007,16 @@
         <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>239</v>
+        <v>288</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>50</v>
@@ -3387,13 +4024,13 @@
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>78</v>
@@ -3405,16 +4042,16 @@
         <v>30</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>244</v>
+        <v>293</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>50</v>
@@ -3422,13 +4059,13 @@
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>78</v>
@@ -3440,7 +4077,7 @@
         <v>30</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>126</v>
@@ -3449,7 +4086,7 @@
         <v>127</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>50</v>
@@ -3457,13 +4094,13 @@
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>78</v>
@@ -3475,16 +4112,16 @@
         <v>30</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>251</v>
+        <v>300</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>50</v>
@@ -3492,13 +4129,13 @@
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>78</v>
@@ -3510,16 +4147,16 @@
         <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>256</v>
+        <v>305</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>257</v>
+        <v>306</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
@@ -3527,13 +4164,13 @@
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>68</v>
@@ -3545,16 +4182,16 @@
         <v>30</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>265</v>
+        <v>314</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>50</v>
@@ -3562,13 +4199,13 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>266</v>
+        <v>315</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>78</v>
@@ -3580,16 +4217,16 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>268</v>
+        <v>317</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>50</v>
@@ -3597,13 +4234,13 @@
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>269</v>
+        <v>318</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>78</v>
@@ -3615,16 +4252,16 @@
         <v>30</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>272</v>
+        <v>321</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>50</v>
@@ -3632,16 +4269,16 @@
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>23</v>
@@ -3650,13 +4287,13 @@
         <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>72</v>
@@ -3667,13 +4304,13 @@
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>211</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>279</v>
+        <v>328</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>213</v>
@@ -3685,13 +4322,13 @@
         <v>30</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>220</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>72</v>
@@ -3702,13 +4339,13 @@
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>281</v>
+        <v>330</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>195</v>
@@ -3720,16 +4357,16 @@
         <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>215</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>283</v>
+        <v>332</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>265</v>
+        <v>314</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>46</v>
@@ -3737,13 +4374,13 @@
     </row>
     <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>78</v>
@@ -3755,16 +4392,16 @@
         <v>30</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>205</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>46</v>
@@ -3772,13 +4409,13 @@
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>78</v>
@@ -3790,13 +4427,13 @@
         <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>215</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>72</v>
@@ -3807,13 +4444,13 @@
     </row>
     <row r="16" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>292</v>
+        <v>341</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>293</v>
+        <v>342</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>195</v>
@@ -3825,13 +4462,13 @@
         <v>30</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>197</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>72</v>
@@ -3902,13 +4539,13 @@
     </row>
     <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>295</v>
+        <v>344</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>296</v>
+        <v>345</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>68</v>
@@ -3920,13 +4557,13 @@
         <v>34</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>72</v>
@@ -3937,13 +4574,13 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>68</v>
@@ -3955,13 +4592,13 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>72</v>
@@ -3972,13 +4609,13 @@
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>303</v>
+        <v>352</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>68</v>
@@ -3990,13 +4627,13 @@
         <v>34</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>72</v>
@@ -4007,13 +4644,13 @@
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>78</v>
@@ -4025,13 +4662,13 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>308</v>
+        <v>357</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>72</v>
@@ -4042,13 +4679,13 @@
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>213</v>
@@ -4060,13 +4697,13 @@
         <v>34</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>72</v>
@@ -4077,13 +4714,13 @@
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>68</v>
@@ -4095,16 +4732,16 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>190</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
@@ -4112,13 +4749,13 @@
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>68</v>
@@ -4130,16 +4767,16 @@
         <v>34</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>321</v>
+        <v>370</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>50</v>
@@ -4147,13 +4784,13 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>373</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>68</v>
@@ -4165,13 +4802,13 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>326</v>
+        <v>375</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>72</v>
@@ -4182,13 +4819,13 @@
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>327</v>
+        <v>376</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>213</v>
@@ -4200,13 +4837,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>72</v>
@@ -4217,13 +4854,13 @@
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>330</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>78</v>
@@ -4235,13 +4872,13 @@
         <v>34</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>333</v>
+        <v>382</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>72</v>
@@ -4252,13 +4889,13 @@
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>335</v>
+        <v>384</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>213</v>
@@ -4270,13 +4907,13 @@
         <v>34</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>205</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>336</v>
+        <v>385</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>72</v>
@@ -4287,13 +4924,13 @@
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>337</v>
+        <v>386</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>195</v>
@@ -4311,10 +4948,10 @@
         <v>197</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>339</v>
+        <v>388</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>50</v>
@@ -4322,13 +4959,13 @@
     </row>
     <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>340</v>
+        <v>389</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>341</v>
+        <v>390</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>213</v>
@@ -4340,13 +4977,13 @@
         <v>34</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>343</v>
+        <v>392</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>72</v>
@@ -4373,7 +5010,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>59</v>
@@ -4384,7 +5021,7 @@
         <v>68</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>345</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4392,7 +5029,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>346</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4400,15 +5037,15 @@
         <v>149</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>347</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>348</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -4416,7 +5053,7 @@
         <v>213</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>349</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4424,7 +5061,7 @@
         <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>350</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -4445,15 +5082,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>352</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>402</v>
       </c>
       <c r="B2" s="5">
         <f>COUNTA('Functional RTM'!A2:A200)</f>
@@ -4461,7 +5098,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>354</v>
+        <v>403</v>
       </c>
       <c r="B3" s="5">
         <f>COUNTA('Security RTM'!A2:A200)</f>
@@ -4469,7 +5106,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>404</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTA('NFR RTM'!A2:A200)</f>
@@ -4477,7 +5114,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>356</v>
+        <v>405</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTA('Functional RTM'!A2:A200)+COUNTA('Security RTM'!A2:A200)+COUNTA('NFR RTM'!A2:A200)</f>
@@ -4485,7 +5122,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Functional RTM'!E2:E200,"M")+COUNTIF('Security RTM'!E2:E200,"M")+COUNTIF('NFR RTM'!E2:E200,"M")</f>
@@ -4501,7 +5138,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Functional RTM'!K2:K200,"Developed")+COUNTIF('Security RTM'!K2:K200,"Developed")+COUNTIF('NFR RTM'!K2:K200,"Developed")</f>
@@ -4509,7 +5146,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="B9" s="5">
         <f>ROUND((COUNTIF('Functional RTM'!K2:K200,"Verified")+COUNTIF('Security RTM'!K2:K200,"Verified")+COUNTIF('NFR RTM'!K2:K200,"Verified"))/(COUNTA('Functional RTM'!A2:A200)+COUNTA('Security RTM'!A2:A200)+COUNTA('NFR RTM'!A2:A200))*100,1)</f>

--- a/docs/PD_RTM_v1.0.xlsx
+++ b/docs/PD_RTM_v1.0.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="454">
   <si>
     <t>PulseDesk — Requirements Traceability Matrix</t>
   </si>
@@ -859,6 +859,123 @@
     <t>TC-F-053</t>
   </si>
   <si>
+    <t>FUN-054</t>
+  </si>
+  <si>
+    <t>Let the user enter either a share quantity or a money amount invested, computing the other from the buy price automatically</t>
+  </si>
+  <si>
+    <t>TC-F-054</t>
+  </si>
+  <si>
+    <t>FUN-055</t>
+  </si>
+  <si>
+    <t>Mutual Funds</t>
+  </si>
+  <si>
+    <t>Show NAV plus 1-day, 1-month and 1-year change for a curated set of popular direct-growth schemes across categories</t>
+  </si>
+  <si>
+    <t>Charter §3.13</t>
+  </si>
+  <si>
+    <t>SDD §4.12</t>
+  </si>
+  <si>
+    <t>TC-F-055</t>
+  </si>
+  <si>
+    <t>FUN-056</t>
+  </si>
+  <si>
+    <t>Filter the fund list by category — Flexi Cap, Large/Mid/Small Cap, Index, Hybrid, Debt</t>
+  </si>
+  <si>
+    <t>TC-F-056</t>
+  </si>
+  <si>
+    <t>FUN-057</t>
+  </si>
+  <si>
+    <t>Let the user expand beyond the top 5 into a ranked list of every stock the scorer scanned</t>
+  </si>
+  <si>
+    <t>TC-F-057</t>
+  </si>
+  <si>
+    <t>FUN-058</t>
+  </si>
+  <si>
+    <t>Stock Detail</t>
+  </si>
+  <si>
+    <t>Show a price history chart for any listed stock across 1D, 5D, 1M, 6M, 1Y and 5Y ranges</t>
+  </si>
+  <si>
+    <t>Charter §3.14</t>
+  </si>
+  <si>
+    <t>SDD §4.13</t>
+  </si>
+  <si>
+    <t>TC-F-058</t>
+  </si>
+  <si>
+    <t>FUN-059</t>
+  </si>
+  <si>
+    <t>Show the most recent related headlines when adding a holding or opening a stock chart</t>
+  </si>
+  <si>
+    <t>TC-F-059</t>
+  </si>
+  <si>
+    <t>FUN-060</t>
+  </si>
+  <si>
+    <t>Filter the popular &amp; steady list by sector</t>
+  </si>
+  <si>
+    <t>TC-F-060</t>
+  </si>
+  <si>
+    <t>FUN-061</t>
+  </si>
+  <si>
+    <t>Predictions</t>
+  </si>
+  <si>
+    <t>Carry a plain-English "likely to rise/fall/stay flat" momentum read on hype rows, the all-scanned list and news items</t>
+  </si>
+  <si>
+    <t>Charter §3.1, §3.3</t>
+  </si>
+  <si>
+    <t>SDD §4.2, §4.4</t>
+  </si>
+  <si>
+    <t>TC-F-061</t>
+  </si>
+  <si>
+    <t>FUN-062</t>
+  </si>
+  <si>
+    <t>Show live conditions for six major financial-hub cities alongside the user own local weather</t>
+  </si>
+  <si>
+    <t>TC-F-062</t>
+  </si>
+  <si>
+    <t>FUN-063</t>
+  </si>
+  <si>
+    <t>State plainly whether each exchange is open now or closed, with a closes-in / opens-in countdown</t>
+  </si>
+  <si>
+    <t>TC-F-063</t>
+  </si>
+  <si>
     <t>SEC-001</t>
   </si>
   <si>
@@ -1051,6 +1168,15 @@
     <t>TC-S-015</t>
   </si>
   <si>
+    <t>SEC-016</t>
+  </si>
+  <si>
+    <t>Mutual fund lookups call only the documented mfapi.in NAV endpoint by a pinned, hardcoded scheme code — no user input is interpolated into the URL</t>
+  </si>
+  <si>
+    <t>TC-S-016</t>
+  </si>
+  <si>
     <t>NFR-001</t>
   </si>
   <si>
@@ -1196,6 +1322,15 @@
   </si>
   <si>
     <t>TC-N-013</t>
+  </si>
+  <si>
+    <t>NFR-014</t>
+  </si>
+  <si>
+    <t>Every predictive or "likely" call is paired with a visible not-investment-advice disclaimer</t>
+  </si>
+  <si>
+    <t>TC-N-014</t>
   </si>
   <si>
     <t>Role</t>
@@ -1986,7 +2121,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3892,6 +4027,356 @@
         <v>50</v>
       </c>
     </row>
+    <row r="55" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3901,7 +4386,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3954,13 +4439,13 @@
     </row>
     <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>78</v>
@@ -3972,16 +4457,16 @@
         <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>50</v>
@@ -3989,13 +4474,13 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>78</v>
@@ -4007,16 +4492,16 @@
         <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>50</v>
@@ -4024,13 +4509,13 @@
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>78</v>
@@ -4042,16 +4527,16 @@
         <v>30</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>50</v>
@@ -4059,13 +4544,13 @@
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>78</v>
@@ -4077,7 +4562,7 @@
         <v>30</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>126</v>
@@ -4086,7 +4571,7 @@
         <v>127</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>50</v>
@@ -4094,13 +4579,13 @@
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>78</v>
@@ -4112,16 +4597,16 @@
         <v>30</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>50</v>
@@ -4129,13 +4614,13 @@
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>78</v>
@@ -4147,16 +4632,16 @@
         <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
@@ -4164,13 +4649,13 @@
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>68</v>
@@ -4182,16 +4667,16 @@
         <v>30</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>50</v>
@@ -4199,13 +4684,13 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>78</v>
@@ -4217,16 +4702,16 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>50</v>
@@ -4234,13 +4719,13 @@
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>78</v>
@@ -4252,16 +4737,16 @@
         <v>30</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>50</v>
@@ -4269,16 +4754,16 @@
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>322</v>
+        <v>361</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>23</v>
@@ -4287,13 +4772,13 @@
         <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>72</v>
@@ -4304,13 +4789,13 @@
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>211</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>213</v>
@@ -4322,13 +4807,13 @@
         <v>30</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>220</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>72</v>
@@ -4339,13 +4824,13 @@
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>195</v>
@@ -4357,16 +4842,16 @@
         <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>215</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>46</v>
@@ -4374,13 +4859,13 @@
     </row>
     <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>78</v>
@@ -4392,16 +4877,16 @@
         <v>30</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>205</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>46</v>
@@ -4409,13 +4894,13 @@
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>78</v>
@@ -4427,13 +4912,13 @@
         <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>215</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>72</v>
@@ -4444,13 +4929,13 @@
     </row>
     <row r="16" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>195</v>
@@ -4462,18 +4947,53 @@
         <v>30</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>197</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>72</v>
       </c>
       <c r="K16" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4486,7 +5006,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -4539,13 +5059,13 @@
     </row>
     <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>68</v>
@@ -4557,13 +5077,13 @@
         <v>34</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>72</v>
@@ -4574,13 +5094,13 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>68</v>
@@ -4592,13 +5112,13 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>72</v>
@@ -4609,13 +5129,13 @@
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>68</v>
@@ -4627,13 +5147,13 @@
         <v>34</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>72</v>
@@ -4644,13 +5164,13 @@
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>397</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>356</v>
+        <v>398</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>78</v>
@@ -4662,13 +5182,13 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>72</v>
@@ -4679,13 +5199,13 @@
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>213</v>
@@ -4697,13 +5217,13 @@
         <v>34</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>72</v>
@@ -4714,13 +5234,13 @@
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>68</v>
@@ -4732,16 +5252,16 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>190</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
@@ -4749,13 +5269,13 @@
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>68</v>
@@ -4767,16 +5287,16 @@
         <v>34</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>50</v>
@@ -4784,13 +5304,13 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>68</v>
@@ -4802,13 +5322,13 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>72</v>
@@ -4819,13 +5339,13 @@
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>213</v>
@@ -4837,13 +5357,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>72</v>
@@ -4854,13 +5374,13 @@
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>78</v>
@@ -4872,13 +5392,13 @@
         <v>34</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>381</v>
+        <v>423</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>72</v>
@@ -4889,13 +5409,13 @@
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>213</v>
@@ -4907,13 +5427,13 @@
         <v>34</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>205</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>72</v>
@@ -4924,13 +5444,13 @@
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>195</v>
@@ -4948,10 +5468,10 @@
         <v>197</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>50</v>
@@ -4959,13 +5479,13 @@
     </row>
     <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>390</v>
+        <v>432</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>213</v>
@@ -4977,18 +5497,53 @@
         <v>34</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>72</v>
       </c>
       <c r="K14" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5010,7 +5565,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>393</v>
+        <v>438</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>59</v>
@@ -5021,7 +5576,7 @@
         <v>68</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>394</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5029,7 +5584,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>395</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5037,15 +5592,15 @@
         <v>149</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>396</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>397</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5053,7 +5608,7 @@
         <v>213</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>398</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5061,7 +5616,7 @@
         <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>399</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -5082,15 +5637,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>401</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="B2" s="5">
         <f>COUNTA('Functional RTM'!A2:A200)</f>
@@ -5098,7 +5653,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="B3" s="5">
         <f>COUNTA('Security RTM'!A2:A200)</f>
@@ -5106,7 +5661,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>404</v>
+        <v>449</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTA('NFR RTM'!A2:A200)</f>
@@ -5114,7 +5669,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTA('Functional RTM'!A2:A200)+COUNTA('Security RTM'!A2:A200)+COUNTA('NFR RTM'!A2:A200)</f>
@@ -5122,7 +5677,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Functional RTM'!E2:E200,"M")+COUNTIF('Security RTM'!E2:E200,"M")+COUNTIF('NFR RTM'!E2:E200,"M")</f>
@@ -5138,7 +5693,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Functional RTM'!K2:K200,"Developed")+COUNTIF('Security RTM'!K2:K200,"Developed")+COUNTIF('NFR RTM'!K2:K200,"Developed")</f>
@@ -5146,7 +5701,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="B9" s="5">
         <f>ROUND((COUNTIF('Functional RTM'!K2:K200,"Verified")+COUNTIF('Security RTM'!K2:K200,"Verified")+COUNTIF('NFR RTM'!K2:K200,"Verified"))/(COUNTA('Functional RTM'!A2:A200)+COUNTA('Security RTM'!A2:A200)+COUNTA('NFR RTM'!A2:A200))*100,1)</f>
